--- a/appium-tests/reports/appium_e2e_test_report.xlsx
+++ b/appium-tests/reports/appium_e2e_test_report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="433">
   <si>
     <t>📱 APPIUM ANDROID E2E MOBILE TEST REPORT</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>22/7/2026, 5:51:25 pm</t>
+    <t>22/7/2026, 6:43:43 pm</t>
   </si>
   <si>
     <t>Target Platform</t>
@@ -47,7 +47,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>0.07 seconds</t>
+    <t>0.05 seconds</t>
   </si>
   <si>
     <t>Test Execution Summary Metrics</t>
@@ -65,7 +65,7 @@
     <t>Pass Rate (%)</t>
   </si>
   <si>
-    <t>80%</t>
+    <t>100%</t>
   </si>
   <si>
     <t>#</t>
@@ -98,7 +98,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>5:51:25 pm</t>
+    <t>6:43:43 pm</t>
   </si>
   <si>
     <t>N/A</t>
@@ -330,12 +330,6 @@
   </si>
   <si>
     <t>TC-EXPLORE-001: Explore Scenario 1: Search &amp; Filter for "Mower" in Category "Outdoor &amp; Camping"</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>homePage.searchResource is not a function</t>
   </si>
   <si>
     <t>TC-EXPLORE-002: Explore Scenario 2: Search &amp; Filter for "Camping Tent" in Category "Electronics &amp; Audio"</t>
@@ -1323,7 +1317,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1365,12 +1359,8 @@
       <b/>
       <color rgb="166534"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="991B1B"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1404,7 +1394,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="DC2626"/>
+        <fgColor rgb="16A34A"/>
       </patternFill>
     </fill>
     <fill>
@@ -1415,11 +1405,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1435,7 +1420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1468,9 +1453,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1925,10 +1907,10 @@
         <v>400</v>
       </c>
       <c r="B13" s="8">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="C13" s="8">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>17</v>
@@ -2047,7 +2029,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>28</v>
@@ -2070,7 +2052,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>28</v>
@@ -2162,7 +2144,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>28</v>
@@ -2231,7 +2213,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>28</v>
@@ -2277,7 +2259,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>28</v>
@@ -2369,7 +2351,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>28</v>
@@ -2645,7 +2627,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>28</v>
@@ -2691,7 +2673,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>28</v>
@@ -2829,7 +2811,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>28</v>
@@ -2852,7 +2834,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>28</v>
@@ -3036,7 +3018,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>28</v>
@@ -3722,8 +3704,8 @@
       <c r="C77" t="s">
         <v>105</v>
       </c>
-      <c r="D77" s="13" t="s">
-        <v>106</v>
+      <c r="D77" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E77" s="12">
         <v>1</v>
@@ -3732,7 +3714,7 @@
         <v>28</v>
       </c>
       <c r="G77" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3743,11 +3725,11 @@
         <v>104</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
-      </c>
-      <c r="D78" s="13" t="s">
         <v>106</v>
       </c>
+      <c r="D78" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="E78" s="12">
         <v>0</v>
       </c>
@@ -3755,7 +3737,7 @@
         <v>28</v>
       </c>
       <c r="G78" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3766,10 +3748,10 @@
         <v>104</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E79" s="12">
         <v>0</v>
@@ -3778,7 +3760,7 @@
         <v>28</v>
       </c>
       <c r="G79" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3789,10 +3771,10 @@
         <v>104</v>
       </c>
       <c r="C80" t="s">
-        <v>110</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E80" s="12">
         <v>0</v>
@@ -3801,7 +3783,7 @@
         <v>28</v>
       </c>
       <c r="G80" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3812,19 +3794,19 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>111</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>106</v>
+        <v>109</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E81" s="12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G81" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3835,10 +3817,10 @@
         <v>104</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E82" s="12">
         <v>0</v>
@@ -3847,7 +3829,7 @@
         <v>28</v>
       </c>
       <c r="G82" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3858,10 +3840,10 @@
         <v>104</v>
       </c>
       <c r="C83" t="s">
-        <v>113</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E83" s="12">
         <v>0</v>
@@ -3870,7 +3852,7 @@
         <v>28</v>
       </c>
       <c r="G83" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3881,10 +3863,10 @@
         <v>104</v>
       </c>
       <c r="C84" t="s">
-        <v>114</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>106</v>
+        <v>112</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E84" s="12">
         <v>0</v>
@@ -3893,7 +3875,7 @@
         <v>28</v>
       </c>
       <c r="G84" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3904,19 +3886,19 @@
         <v>104</v>
       </c>
       <c r="C85" t="s">
-        <v>115</v>
-      </c>
-      <c r="D85" s="13" t="s">
-        <v>106</v>
+        <v>113</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E85" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G85" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3927,10 +3909,10 @@
         <v>104</v>
       </c>
       <c r="C86" t="s">
-        <v>116</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>106</v>
+        <v>114</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E86" s="12">
         <v>0</v>
@@ -3939,7 +3921,7 @@
         <v>28</v>
       </c>
       <c r="G86" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3950,10 +3932,10 @@
         <v>104</v>
       </c>
       <c r="C87" t="s">
-        <v>117</v>
-      </c>
-      <c r="D87" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E87" s="12">
         <v>0</v>
@@ -3962,7 +3944,7 @@
         <v>28</v>
       </c>
       <c r="G87" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3973,10 +3955,10 @@
         <v>104</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>106</v>
+        <v>116</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E88" s="12">
         <v>0</v>
@@ -3985,7 +3967,7 @@
         <v>28</v>
       </c>
       <c r="G88" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3996,10 +3978,10 @@
         <v>104</v>
       </c>
       <c r="C89" t="s">
-        <v>119</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>106</v>
+        <v>117</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E89" s="12">
         <v>0</v>
@@ -4008,7 +3990,7 @@
         <v>28</v>
       </c>
       <c r="G89" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4019,10 +4001,10 @@
         <v>104</v>
       </c>
       <c r="C90" t="s">
-        <v>120</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>106</v>
+        <v>118</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E90" s="12">
         <v>0</v>
@@ -4031,7 +4013,7 @@
         <v>28</v>
       </c>
       <c r="G90" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4042,10 +4024,10 @@
         <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>121</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>106</v>
+        <v>119</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E91" s="12">
         <v>0</v>
@@ -4054,7 +4036,7 @@
         <v>28</v>
       </c>
       <c r="G91" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4065,10 +4047,10 @@
         <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>106</v>
+        <v>120</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E92" s="12">
         <v>0</v>
@@ -4077,7 +4059,7 @@
         <v>28</v>
       </c>
       <c r="G92" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4088,10 +4070,10 @@
         <v>104</v>
       </c>
       <c r="C93" t="s">
-        <v>123</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>106</v>
+        <v>121</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E93" s="12">
         <v>0</v>
@@ -4100,7 +4082,7 @@
         <v>28</v>
       </c>
       <c r="G93" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4111,10 +4093,10 @@
         <v>104</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>106</v>
+        <v>122</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E94" s="12">
         <v>0</v>
@@ -4123,7 +4105,7 @@
         <v>28</v>
       </c>
       <c r="G94" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4134,10 +4116,10 @@
         <v>104</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>106</v>
+        <v>123</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E95" s="12">
         <v>0</v>
@@ -4146,7 +4128,7 @@
         <v>28</v>
       </c>
       <c r="G95" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4157,10 +4139,10 @@
         <v>104</v>
       </c>
       <c r="C96" t="s">
-        <v>126</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>106</v>
+        <v>124</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E96" s="12">
         <v>0</v>
@@ -4169,7 +4151,7 @@
         <v>28</v>
       </c>
       <c r="G96" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4180,10 +4162,10 @@
         <v>104</v>
       </c>
       <c r="C97" t="s">
-        <v>127</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>106</v>
+        <v>125</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E97" s="12">
         <v>0</v>
@@ -4192,7 +4174,7 @@
         <v>28</v>
       </c>
       <c r="G97" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4203,10 +4185,10 @@
         <v>104</v>
       </c>
       <c r="C98" t="s">
-        <v>128</v>
-      </c>
-      <c r="D98" s="13" t="s">
-        <v>106</v>
+        <v>126</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E98" s="12">
         <v>0</v>
@@ -4215,7 +4197,7 @@
         <v>28</v>
       </c>
       <c r="G98" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4226,10 +4208,10 @@
         <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>129</v>
-      </c>
-      <c r="D99" s="13" t="s">
-        <v>106</v>
+        <v>127</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E99" s="12">
         <v>0</v>
@@ -4238,7 +4220,7 @@
         <v>28</v>
       </c>
       <c r="G99" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4249,10 +4231,10 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>130</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>106</v>
+        <v>128</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E100" s="12">
         <v>0</v>
@@ -4261,7 +4243,7 @@
         <v>28</v>
       </c>
       <c r="G100" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4272,10 +4254,10 @@
         <v>104</v>
       </c>
       <c r="C101" t="s">
-        <v>131</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>106</v>
+        <v>129</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E101" s="12">
         <v>0</v>
@@ -4284,7 +4266,7 @@
         <v>28</v>
       </c>
       <c r="G101" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4295,10 +4277,10 @@
         <v>104</v>
       </c>
       <c r="C102" t="s">
-        <v>132</v>
-      </c>
-      <c r="D102" s="13" t="s">
-        <v>106</v>
+        <v>130</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E102" s="12">
         <v>0</v>
@@ -4307,7 +4289,7 @@
         <v>28</v>
       </c>
       <c r="G102" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4318,10 +4300,10 @@
         <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>133</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>106</v>
+        <v>131</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E103" s="12">
         <v>0</v>
@@ -4330,7 +4312,7 @@
         <v>28</v>
       </c>
       <c r="G103" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4341,10 +4323,10 @@
         <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>134</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>106</v>
+        <v>132</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E104" s="12">
         <v>0</v>
@@ -4353,7 +4335,7 @@
         <v>28</v>
       </c>
       <c r="G104" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4364,10 +4346,10 @@
         <v>104</v>
       </c>
       <c r="C105" t="s">
-        <v>135</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>106</v>
+        <v>133</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E105" s="12">
         <v>0</v>
@@ -4376,7 +4358,7 @@
         <v>28</v>
       </c>
       <c r="G105" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4387,10 +4369,10 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>136</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>106</v>
+        <v>134</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E106" s="12">
         <v>0</v>
@@ -4399,7 +4381,7 @@
         <v>28</v>
       </c>
       <c r="G106" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4410,10 +4392,10 @@
         <v>104</v>
       </c>
       <c r="C107" t="s">
-        <v>137</v>
-      </c>
-      <c r="D107" s="13" t="s">
-        <v>106</v>
+        <v>135</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E107" s="12">
         <v>0</v>
@@ -4422,7 +4404,7 @@
         <v>28</v>
       </c>
       <c r="G107" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4433,19 +4415,19 @@
         <v>104</v>
       </c>
       <c r="C108" t="s">
-        <v>138</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>106</v>
+        <v>136</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E108" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F108" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4456,10 +4438,10 @@
         <v>104</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>106</v>
+        <v>137</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E109" s="12">
         <v>0</v>
@@ -4468,7 +4450,7 @@
         <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4479,10 +4461,10 @@
         <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>140</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>106</v>
+        <v>138</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E110" s="12">
         <v>0</v>
@@ -4491,7 +4473,7 @@
         <v>28</v>
       </c>
       <c r="G110" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4502,10 +4484,10 @@
         <v>104</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>106</v>
+        <v>139</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E111" s="12">
         <v>0</v>
@@ -4514,7 +4496,7 @@
         <v>28</v>
       </c>
       <c r="G111" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4525,10 +4507,10 @@
         <v>104</v>
       </c>
       <c r="C112" t="s">
-        <v>142</v>
-      </c>
-      <c r="D112" s="13" t="s">
-        <v>106</v>
+        <v>140</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E112" s="12">
         <v>0</v>
@@ -4537,7 +4519,7 @@
         <v>28</v>
       </c>
       <c r="G112" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4548,10 +4530,10 @@
         <v>104</v>
       </c>
       <c r="C113" t="s">
-        <v>143</v>
-      </c>
-      <c r="D113" s="13" t="s">
-        <v>106</v>
+        <v>141</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E113" s="12">
         <v>0</v>
@@ -4560,7 +4542,7 @@
         <v>28</v>
       </c>
       <c r="G113" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4571,10 +4553,10 @@
         <v>104</v>
       </c>
       <c r="C114" t="s">
-        <v>144</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>106</v>
+        <v>142</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E114" s="12">
         <v>0</v>
@@ -4583,7 +4565,7 @@
         <v>28</v>
       </c>
       <c r="G114" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4594,10 +4576,10 @@
         <v>104</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>106</v>
+        <v>143</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E115" s="12">
         <v>0</v>
@@ -4606,7 +4588,7 @@
         <v>28</v>
       </c>
       <c r="G115" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4617,10 +4599,10 @@
         <v>104</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
-      </c>
-      <c r="D116" s="13" t="s">
-        <v>106</v>
+        <v>144</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E116" s="12">
         <v>0</v>
@@ -4629,7 +4611,7 @@
         <v>28</v>
       </c>
       <c r="G116" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4640,10 +4622,10 @@
         <v>104</v>
       </c>
       <c r="C117" t="s">
-        <v>147</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>106</v>
+        <v>145</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E117" s="12">
         <v>0</v>
@@ -4652,7 +4634,7 @@
         <v>28</v>
       </c>
       <c r="G117" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4663,10 +4645,10 @@
         <v>104</v>
       </c>
       <c r="C118" t="s">
-        <v>148</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>106</v>
+        <v>146</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E118" s="12">
         <v>0</v>
@@ -4675,7 +4657,7 @@
         <v>28</v>
       </c>
       <c r="G118" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4686,10 +4668,10 @@
         <v>104</v>
       </c>
       <c r="C119" t="s">
-        <v>149</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>106</v>
+        <v>147</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E119" s="12">
         <v>0</v>
@@ -4698,7 +4680,7 @@
         <v>28</v>
       </c>
       <c r="G119" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4709,10 +4691,10 @@
         <v>104</v>
       </c>
       <c r="C120" t="s">
-        <v>150</v>
-      </c>
-      <c r="D120" s="13" t="s">
-        <v>106</v>
+        <v>148</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E120" s="12">
         <v>0</v>
@@ -4721,7 +4703,7 @@
         <v>28</v>
       </c>
       <c r="G120" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4732,19 +4714,19 @@
         <v>104</v>
       </c>
       <c r="C121" t="s">
-        <v>151</v>
-      </c>
-      <c r="D121" s="13" t="s">
-        <v>106</v>
+        <v>149</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E121" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G121" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4755,10 +4737,10 @@
         <v>104</v>
       </c>
       <c r="C122" t="s">
-        <v>152</v>
-      </c>
-      <c r="D122" s="13" t="s">
-        <v>106</v>
+        <v>150</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E122" s="12">
         <v>0</v>
@@ -4767,7 +4749,7 @@
         <v>28</v>
       </c>
       <c r="G122" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4778,10 +4760,10 @@
         <v>104</v>
       </c>
       <c r="C123" t="s">
-        <v>153</v>
-      </c>
-      <c r="D123" s="13" t="s">
-        <v>106</v>
+        <v>151</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E123" s="12">
         <v>0</v>
@@ -4790,7 +4772,7 @@
         <v>28</v>
       </c>
       <c r="G123" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4801,19 +4783,19 @@
         <v>104</v>
       </c>
       <c r="C124" t="s">
-        <v>154</v>
-      </c>
-      <c r="D124" s="13" t="s">
-        <v>106</v>
+        <v>152</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E124" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G124" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4824,19 +4806,19 @@
         <v>104</v>
       </c>
       <c r="C125" t="s">
-        <v>155</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>106</v>
+        <v>153</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E125" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G125" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4847,10 +4829,10 @@
         <v>104</v>
       </c>
       <c r="C126" t="s">
-        <v>156</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>106</v>
+        <v>154</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E126" s="12">
         <v>0</v>
@@ -4859,7 +4841,7 @@
         <v>28</v>
       </c>
       <c r="G126" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4870,10 +4852,10 @@
         <v>104</v>
       </c>
       <c r="C127" t="s">
-        <v>157</v>
-      </c>
-      <c r="D127" s="13" t="s">
-        <v>106</v>
+        <v>155</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E127" s="12">
         <v>0</v>
@@ -4882,7 +4864,7 @@
         <v>28</v>
       </c>
       <c r="G127" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4893,10 +4875,10 @@
         <v>104</v>
       </c>
       <c r="C128" t="s">
-        <v>158</v>
-      </c>
-      <c r="D128" s="13" t="s">
-        <v>106</v>
+        <v>156</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E128" s="12">
         <v>0</v>
@@ -4905,7 +4887,7 @@
         <v>28</v>
       </c>
       <c r="G128" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4916,19 +4898,19 @@
         <v>104</v>
       </c>
       <c r="C129" t="s">
-        <v>159</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>106</v>
+        <v>157</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E129" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G129" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4939,10 +4921,10 @@
         <v>104</v>
       </c>
       <c r="C130" t="s">
-        <v>160</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>106</v>
+        <v>158</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E130" s="12">
         <v>0</v>
@@ -4951,7 +4933,7 @@
         <v>28</v>
       </c>
       <c r="G130" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4962,10 +4944,10 @@
         <v>104</v>
       </c>
       <c r="C131" t="s">
-        <v>161</v>
-      </c>
-      <c r="D131" s="13" t="s">
-        <v>106</v>
+        <v>159</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E131" s="12">
         <v>0</v>
@@ -4974,7 +4956,7 @@
         <v>28</v>
       </c>
       <c r="G131" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4985,10 +4967,10 @@
         <v>104</v>
       </c>
       <c r="C132" t="s">
-        <v>162</v>
-      </c>
-      <c r="D132" s="13" t="s">
-        <v>106</v>
+        <v>160</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E132" s="12">
         <v>0</v>
@@ -4997,7 +4979,7 @@
         <v>28</v>
       </c>
       <c r="G132" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5008,10 +4990,10 @@
         <v>104</v>
       </c>
       <c r="C133" t="s">
-        <v>163</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>106</v>
+        <v>161</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E133" s="12">
         <v>0</v>
@@ -5020,7 +5002,7 @@
         <v>28</v>
       </c>
       <c r="G133" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5031,10 +5013,10 @@
         <v>104</v>
       </c>
       <c r="C134" t="s">
-        <v>164</v>
-      </c>
-      <c r="D134" s="13" t="s">
-        <v>106</v>
+        <v>162</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E134" s="12">
         <v>0</v>
@@ -5043,7 +5025,7 @@
         <v>28</v>
       </c>
       <c r="G134" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5054,19 +5036,19 @@
         <v>104</v>
       </c>
       <c r="C135" t="s">
-        <v>165</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>106</v>
+        <v>163</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E135" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G135" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="136" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5077,10 +5059,10 @@
         <v>104</v>
       </c>
       <c r="C136" t="s">
-        <v>166</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>106</v>
+        <v>164</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E136" s="12">
         <v>0</v>
@@ -5089,7 +5071,7 @@
         <v>28</v>
       </c>
       <c r="G136" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="137" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5100,10 +5082,10 @@
         <v>104</v>
       </c>
       <c r="C137" t="s">
-        <v>167</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>106</v>
+        <v>165</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E137" s="12">
         <v>0</v>
@@ -5112,7 +5094,7 @@
         <v>28</v>
       </c>
       <c r="G137" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5123,10 +5105,10 @@
         <v>104</v>
       </c>
       <c r="C138" t="s">
-        <v>168</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>106</v>
+        <v>166</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E138" s="12">
         <v>0</v>
@@ -5135,7 +5117,7 @@
         <v>28</v>
       </c>
       <c r="G138" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="139" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5146,10 +5128,10 @@
         <v>104</v>
       </c>
       <c r="C139" t="s">
-        <v>169</v>
-      </c>
-      <c r="D139" s="13" t="s">
-        <v>106</v>
+        <v>167</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E139" s="12">
         <v>0</v>
@@ -5158,7 +5140,7 @@
         <v>28</v>
       </c>
       <c r="G139" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="140" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5169,10 +5151,10 @@
         <v>104</v>
       </c>
       <c r="C140" t="s">
-        <v>170</v>
-      </c>
-      <c r="D140" s="13" t="s">
-        <v>106</v>
+        <v>168</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E140" s="12">
         <v>0</v>
@@ -5181,7 +5163,7 @@
         <v>28</v>
       </c>
       <c r="G140" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5192,10 +5174,10 @@
         <v>104</v>
       </c>
       <c r="C141" t="s">
-        <v>171</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>106</v>
+        <v>169</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E141" s="12">
         <v>0</v>
@@ -5204,7 +5186,7 @@
         <v>28</v>
       </c>
       <c r="G141" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5215,10 +5197,10 @@
         <v>104</v>
       </c>
       <c r="C142" t="s">
-        <v>172</v>
-      </c>
-      <c r="D142" s="13" t="s">
-        <v>106</v>
+        <v>170</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E142" s="12">
         <v>0</v>
@@ -5227,7 +5209,7 @@
         <v>28</v>
       </c>
       <c r="G142" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="143" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5238,10 +5220,10 @@
         <v>104</v>
       </c>
       <c r="C143" t="s">
-        <v>173</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>106</v>
+        <v>171</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E143" s="12">
         <v>0</v>
@@ -5250,7 +5232,7 @@
         <v>28</v>
       </c>
       <c r="G143" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="144" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5261,10 +5243,10 @@
         <v>104</v>
       </c>
       <c r="C144" t="s">
-        <v>174</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>106</v>
+        <v>172</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E144" s="12">
         <v>0</v>
@@ -5273,7 +5255,7 @@
         <v>28</v>
       </c>
       <c r="G144" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5284,19 +5266,19 @@
         <v>104</v>
       </c>
       <c r="C145" t="s">
-        <v>175</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>106</v>
+        <v>173</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E145" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G145" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="146" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5307,10 +5289,10 @@
         <v>104</v>
       </c>
       <c r="C146" t="s">
-        <v>176</v>
-      </c>
-      <c r="D146" s="13" t="s">
-        <v>106</v>
+        <v>174</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E146" s="12">
         <v>0</v>
@@ -5319,7 +5301,7 @@
         <v>28</v>
       </c>
       <c r="G146" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="147" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5330,19 +5312,19 @@
         <v>104</v>
       </c>
       <c r="C147" t="s">
-        <v>177</v>
-      </c>
-      <c r="D147" s="13" t="s">
-        <v>106</v>
+        <v>175</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E147" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>28</v>
       </c>
       <c r="G147" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5353,10 +5335,10 @@
         <v>104</v>
       </c>
       <c r="C148" t="s">
-        <v>178</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>106</v>
+        <v>176</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E148" s="12">
         <v>0</v>
@@ -5365,7 +5347,7 @@
         <v>28</v>
       </c>
       <c r="G148" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="149" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5376,10 +5358,10 @@
         <v>104</v>
       </c>
       <c r="C149" t="s">
-        <v>179</v>
-      </c>
-      <c r="D149" s="13" t="s">
-        <v>106</v>
+        <v>177</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E149" s="12">
         <v>0</v>
@@ -5388,7 +5370,7 @@
         <v>28</v>
       </c>
       <c r="G149" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="150" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5399,10 +5381,10 @@
         <v>104</v>
       </c>
       <c r="C150" t="s">
-        <v>180</v>
-      </c>
-      <c r="D150" s="13" t="s">
-        <v>106</v>
+        <v>178</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E150" s="12">
         <v>0</v>
@@ -5411,7 +5393,7 @@
         <v>28</v>
       </c>
       <c r="G150" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5422,10 +5404,10 @@
         <v>104</v>
       </c>
       <c r="C151" t="s">
-        <v>181</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>106</v>
+        <v>179</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E151" s="12">
         <v>0</v>
@@ -5434,7 +5416,7 @@
         <v>28</v>
       </c>
       <c r="G151" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="152" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5445,10 +5427,10 @@
         <v>104</v>
       </c>
       <c r="C152" t="s">
-        <v>182</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>106</v>
+        <v>180</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E152" s="12">
         <v>0</v>
@@ -5457,7 +5439,7 @@
         <v>28</v>
       </c>
       <c r="G152" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="153" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5468,10 +5450,10 @@
         <v>104</v>
       </c>
       <c r="C153" t="s">
-        <v>183</v>
-      </c>
-      <c r="D153" s="13" t="s">
-        <v>106</v>
+        <v>181</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E153" s="12">
         <v>0</v>
@@ -5480,7 +5462,7 @@
         <v>28</v>
       </c>
       <c r="G153" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="154" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5491,10 +5473,10 @@
         <v>104</v>
       </c>
       <c r="C154" t="s">
-        <v>184</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>106</v>
+        <v>182</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E154" s="12">
         <v>0</v>
@@ -5503,7 +5485,7 @@
         <v>28</v>
       </c>
       <c r="G154" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="155" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5514,10 +5496,10 @@
         <v>104</v>
       </c>
       <c r="C155" t="s">
-        <v>185</v>
-      </c>
-      <c r="D155" s="13" t="s">
-        <v>106</v>
+        <v>183</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E155" s="12">
         <v>0</v>
@@ -5526,7 +5508,7 @@
         <v>28</v>
       </c>
       <c r="G155" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="156" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5537,10 +5519,10 @@
         <v>104</v>
       </c>
       <c r="C156" t="s">
-        <v>186</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>106</v>
+        <v>184</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="E156" s="12">
         <v>0</v>
@@ -5549,7 +5531,7 @@
         <v>28</v>
       </c>
       <c r="G156" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="157" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5557,10 +5539,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C157" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D157" s="11" t="s">
         <v>27</v>
@@ -5580,10 +5562,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>185</v>
+      </c>
+      <c r="C158" t="s">
         <v>187</v>
-      </c>
-      <c r="C158" t="s">
-        <v>189</v>
       </c>
       <c r="D158" s="11" t="s">
         <v>27</v>
@@ -5603,10 +5585,10 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C159" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D159" s="11" t="s">
         <v>27</v>
@@ -5626,10 +5608,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C160" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D160" s="11" t="s">
         <v>27</v>
@@ -5649,16 +5631,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C161" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D161" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E161" s="12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>28</v>
@@ -5672,10 +5654,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D162" s="11" t="s">
         <v>27</v>
@@ -5695,10 +5677,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C163" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D163" s="11" t="s">
         <v>27</v>
@@ -5718,10 +5700,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C164" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D164" s="11" t="s">
         <v>27</v>
@@ -5741,16 +5723,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C165" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D165" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E165" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>28</v>
@@ -5764,10 +5746,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C166" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D166" s="11" t="s">
         <v>27</v>
@@ -5787,10 +5769,10 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C167" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D167" s="11" t="s">
         <v>27</v>
@@ -5810,10 +5792,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C168" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D168" s="11" t="s">
         <v>27</v>
@@ -5833,10 +5815,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C169" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D169" s="11" t="s">
         <v>27</v>
@@ -5856,10 +5838,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C170" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D170" s="11" t="s">
         <v>27</v>
@@ -5879,10 +5861,10 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C171" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D171" s="11" t="s">
         <v>27</v>
@@ -5902,10 +5884,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C172" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D172" s="11" t="s">
         <v>27</v>
@@ -5925,10 +5907,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C173" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D173" s="11" t="s">
         <v>27</v>
@@ -5948,10 +5930,10 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C174" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D174" s="11" t="s">
         <v>27</v>
@@ -5971,10 +5953,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C175" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D175" s="11" t="s">
         <v>27</v>
@@ -5994,10 +5976,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C176" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D176" s="11" t="s">
         <v>27</v>
@@ -6017,10 +5999,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C177" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D177" s="11" t="s">
         <v>27</v>
@@ -6040,10 +6022,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C178" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D178" s="11" t="s">
         <v>27</v>
@@ -6063,10 +6045,10 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C179" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D179" s="11" t="s">
         <v>27</v>
@@ -6086,10 +6068,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C180" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D180" s="11" t="s">
         <v>27</v>
@@ -6109,10 +6091,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D181" s="11" t="s">
         <v>27</v>
@@ -6132,16 +6114,16 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C182" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D182" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E182" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F182" s="10" t="s">
         <v>28</v>
@@ -6155,10 +6137,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C183" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D183" s="11" t="s">
         <v>27</v>
@@ -6178,10 +6160,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C184" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D184" s="11" t="s">
         <v>27</v>
@@ -6201,10 +6183,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C185" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D185" s="11" t="s">
         <v>27</v>
@@ -6224,10 +6206,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C186" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D186" s="11" t="s">
         <v>27</v>
@@ -6247,10 +6229,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C187" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D187" s="11" t="s">
         <v>27</v>
@@ -6270,10 +6252,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C188" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D188" s="11" t="s">
         <v>27</v>
@@ -6293,10 +6275,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C189" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D189" s="11" t="s">
         <v>27</v>
@@ -6316,10 +6298,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C190" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D190" s="11" t="s">
         <v>27</v>
@@ -6339,10 +6321,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C191" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D191" s="11" t="s">
         <v>27</v>
@@ -6362,10 +6344,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C192" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D192" s="11" t="s">
         <v>27</v>
@@ -6385,10 +6367,10 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C193" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D193" s="11" t="s">
         <v>27</v>
@@ -6408,10 +6390,10 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C194" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D194" s="11" t="s">
         <v>27</v>
@@ -6431,10 +6413,10 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C195" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D195" s="11" t="s">
         <v>27</v>
@@ -6454,10 +6436,10 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C196" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D196" s="11" t="s">
         <v>27</v>
@@ -6477,10 +6459,10 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C197" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D197" s="11" t="s">
         <v>27</v>
@@ -6500,10 +6482,10 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C198" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D198" s="11" t="s">
         <v>27</v>
@@ -6523,10 +6505,10 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C199" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D199" s="11" t="s">
         <v>27</v>
@@ -6546,10 +6528,10 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C200" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D200" s="11" t="s">
         <v>27</v>
@@ -6569,16 +6551,16 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C201" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D201" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E201" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>28</v>
@@ -6592,10 +6574,10 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C202" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D202" s="11" t="s">
         <v>27</v>
@@ -6615,16 +6597,16 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C203" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D203" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E203" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>28</v>
@@ -6638,10 +6620,10 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C204" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D204" s="11" t="s">
         <v>27</v>
@@ -6661,16 +6643,16 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C205" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D205" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E205" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>28</v>
@@ -6684,10 +6666,10 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C206" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D206" s="11" t="s">
         <v>27</v>
@@ -6707,10 +6689,10 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C207" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D207" s="11" t="s">
         <v>27</v>
@@ -6730,10 +6712,10 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C208" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D208" s="11" t="s">
         <v>27</v>
@@ -6753,10 +6735,10 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C209" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D209" s="11" t="s">
         <v>27</v>
@@ -6776,10 +6758,10 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C210" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D210" s="11" t="s">
         <v>27</v>
@@ -6799,10 +6781,10 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C211" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D211" s="11" t="s">
         <v>27</v>
@@ -6822,10 +6804,10 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C212" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D212" s="11" t="s">
         <v>27</v>
@@ -6845,16 +6827,16 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C213" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D213" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E213" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>28</v>
@@ -6868,10 +6850,10 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C214" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D214" s="11" t="s">
         <v>27</v>
@@ -6891,10 +6873,10 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C215" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D215" s="11" t="s">
         <v>27</v>
@@ -6914,10 +6896,10 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C216" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D216" s="11" t="s">
         <v>27</v>
@@ -6937,10 +6919,10 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C217" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D217" s="11" t="s">
         <v>27</v>
@@ -6960,10 +6942,10 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C218" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D218" s="11" t="s">
         <v>27</v>
@@ -6983,10 +6965,10 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C219" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D219" s="11" t="s">
         <v>27</v>
@@ -7006,10 +6988,10 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C220" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D220" s="11" t="s">
         <v>27</v>
@@ -7029,10 +7011,10 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C221" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D221" s="11" t="s">
         <v>27</v>
@@ -7052,10 +7034,10 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C222" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D222" s="11" t="s">
         <v>27</v>
@@ -7075,10 +7057,10 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C223" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D223" s="11" t="s">
         <v>27</v>
@@ -7098,10 +7080,10 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C224" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D224" s="11" t="s">
         <v>27</v>
@@ -7121,16 +7103,16 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C225" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D225" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E225" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>28</v>
@@ -7144,10 +7126,10 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C226" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D226" s="11" t="s">
         <v>27</v>
@@ -7167,10 +7149,10 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C227" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D227" s="11" t="s">
         <v>27</v>
@@ -7190,10 +7172,10 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D228" s="11" t="s">
         <v>27</v>
@@ -7213,10 +7195,10 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C229" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D229" s="11" t="s">
         <v>27</v>
@@ -7236,10 +7218,10 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C230" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D230" s="11" t="s">
         <v>27</v>
@@ -7259,10 +7241,10 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C231" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D231" s="11" t="s">
         <v>27</v>
@@ -7282,10 +7264,10 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C232" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D232" s="11" t="s">
         <v>27</v>
@@ -7305,10 +7287,10 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C233" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D233" s="11" t="s">
         <v>27</v>
@@ -7328,10 +7310,10 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C234" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D234" s="11" t="s">
         <v>27</v>
@@ -7351,10 +7333,10 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C235" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D235" s="11" t="s">
         <v>27</v>
@@ -7374,10 +7356,10 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C236" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D236" s="11" t="s">
         <v>27</v>
@@ -7397,10 +7379,10 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C237" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D237" s="11" t="s">
         <v>27</v>
@@ -7420,10 +7402,10 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C238" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D238" s="11" t="s">
         <v>27</v>
@@ -7443,10 +7425,10 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C239" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D239" s="11" t="s">
         <v>27</v>
@@ -7466,10 +7448,10 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C240" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D240" s="11" t="s">
         <v>27</v>
@@ -7489,10 +7471,10 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C241" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D241" s="11" t="s">
         <v>27</v>
@@ -7512,10 +7494,10 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C242" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D242" s="11" t="s">
         <v>27</v>
@@ -7535,10 +7517,10 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C243" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D243" s="11" t="s">
         <v>27</v>
@@ -7558,10 +7540,10 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C244" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D244" s="11" t="s">
         <v>27</v>
@@ -7581,10 +7563,10 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C245" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D245" s="11" t="s">
         <v>27</v>
@@ -7604,10 +7586,10 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C246" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D246" s="11" t="s">
         <v>27</v>
@@ -7627,16 +7609,16 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C247" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D247" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E247" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>28</v>
@@ -7650,10 +7632,10 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
+        <v>276</v>
+      </c>
+      <c r="C248" t="s">
         <v>278</v>
-      </c>
-      <c r="C248" t="s">
-        <v>280</v>
       </c>
       <c r="D248" s="11" t="s">
         <v>27</v>
@@ -7673,10 +7655,10 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C249" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D249" s="11" t="s">
         <v>27</v>
@@ -7696,10 +7678,10 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C250" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D250" s="11" t="s">
         <v>27</v>
@@ -7719,10 +7701,10 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C251" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D251" s="11" t="s">
         <v>27</v>
@@ -7742,16 +7724,16 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C252" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D252" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E252" s="12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F252" s="10" t="s">
         <v>28</v>
@@ -7765,10 +7747,10 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D253" s="11" t="s">
         <v>27</v>
@@ -7788,10 +7770,10 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C254" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D254" s="11" t="s">
         <v>27</v>
@@ -7811,10 +7793,10 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C255" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D255" s="11" t="s">
         <v>27</v>
@@ -7834,10 +7816,10 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C256" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D256" s="11" t="s">
         <v>27</v>
@@ -7857,16 +7839,16 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C257" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D257" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E257" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>28</v>
@@ -7880,10 +7862,10 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C258" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D258" s="11" t="s">
         <v>27</v>
@@ -7903,10 +7885,10 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C259" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D259" s="11" t="s">
         <v>27</v>
@@ -7926,10 +7908,10 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C260" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D260" s="11" t="s">
         <v>27</v>
@@ -7949,10 +7931,10 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C261" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D261" s="11" t="s">
         <v>27</v>
@@ -7972,10 +7954,10 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C262" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D262" s="11" t="s">
         <v>27</v>
@@ -7995,10 +7977,10 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C263" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D263" s="11" t="s">
         <v>27</v>
@@ -8018,10 +8000,10 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C264" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D264" s="11" t="s">
         <v>27</v>
@@ -8041,10 +8023,10 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C265" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D265" s="11" t="s">
         <v>27</v>
@@ -8064,10 +8046,10 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C266" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D266" s="11" t="s">
         <v>27</v>
@@ -8087,10 +8069,10 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C267" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D267" s="11" t="s">
         <v>27</v>
@@ -8110,10 +8092,10 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C268" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D268" s="11" t="s">
         <v>27</v>
@@ -8133,10 +8115,10 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C269" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D269" s="11" t="s">
         <v>27</v>
@@ -8156,10 +8138,10 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C270" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D270" s="11" t="s">
         <v>27</v>
@@ -8179,10 +8161,10 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C271" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D271" s="11" t="s">
         <v>27</v>
@@ -8202,10 +8184,10 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C272" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D272" s="11" t="s">
         <v>27</v>
@@ -8225,10 +8207,10 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C273" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D273" s="11" t="s">
         <v>27</v>
@@ -8248,10 +8230,10 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C274" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D274" s="11" t="s">
         <v>27</v>
@@ -8271,10 +8253,10 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C275" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D275" s="11" t="s">
         <v>27</v>
@@ -8294,10 +8276,10 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C276" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D276" s="11" t="s">
         <v>27</v>
@@ -8317,10 +8299,10 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C277" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D277" s="11" t="s">
         <v>27</v>
@@ -8340,16 +8322,16 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C278" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D278" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E278" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F278" s="10" t="s">
         <v>28</v>
@@ -8363,10 +8345,10 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C279" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D279" s="11" t="s">
         <v>27</v>
@@ -8386,10 +8368,10 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C280" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D280" s="11" t="s">
         <v>27</v>
@@ -8409,10 +8391,10 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C281" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D281" s="11" t="s">
         <v>27</v>
@@ -8432,10 +8414,10 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C282" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D282" s="11" t="s">
         <v>27</v>
@@ -8455,10 +8437,10 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C283" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D283" s="11" t="s">
         <v>27</v>
@@ -8478,10 +8460,10 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C284" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D284" s="11" t="s">
         <v>27</v>
@@ -8501,10 +8483,10 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C285" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D285" s="11" t="s">
         <v>27</v>
@@ -8524,10 +8506,10 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C286" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D286" s="11" t="s">
         <v>27</v>
@@ -8547,10 +8529,10 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C287" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D287" s="11" t="s">
         <v>27</v>
@@ -8570,10 +8552,10 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C288" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D288" s="11" t="s">
         <v>27</v>
@@ -8593,10 +8575,10 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C289" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D289" s="11" t="s">
         <v>27</v>
@@ -8616,10 +8598,10 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C290" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D290" s="11" t="s">
         <v>27</v>
@@ -8639,10 +8621,10 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C291" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D291" s="11" t="s">
         <v>27</v>
@@ -8662,10 +8644,10 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C292" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D292" s="11" t="s">
         <v>27</v>
@@ -8685,10 +8667,10 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C293" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D293" s="11" t="s">
         <v>27</v>
@@ -8708,16 +8690,16 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C294" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D294" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E294" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F294" s="10" t="s">
         <v>28</v>
@@ -8731,10 +8713,10 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C295" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D295" s="11" t="s">
         <v>27</v>
@@ -8754,10 +8736,10 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C296" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D296" s="11" t="s">
         <v>27</v>
@@ -8777,10 +8759,10 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C297" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D297" s="11" t="s">
         <v>27</v>
@@ -8800,10 +8782,10 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C298" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D298" s="11" t="s">
         <v>27</v>
@@ -8823,10 +8805,10 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C299" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D299" s="11" t="s">
         <v>27</v>
@@ -8846,10 +8828,10 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C300" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D300" s="11" t="s">
         <v>27</v>
@@ -8869,10 +8851,10 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C301" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D301" s="11" t="s">
         <v>27</v>
@@ -8892,10 +8874,10 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C302" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D302" s="11" t="s">
         <v>27</v>
@@ -8915,10 +8897,10 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C303" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D303" s="11" t="s">
         <v>27</v>
@@ -8938,10 +8920,10 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C304" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D304" s="11" t="s">
         <v>27</v>
@@ -8961,16 +8943,16 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C305" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D305" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E305" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F305" s="10" t="s">
         <v>28</v>
@@ -8984,10 +8966,10 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C306" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D306" s="11" t="s">
         <v>27</v>
@@ -9007,16 +8989,16 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C307" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D307" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E307" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F307" s="10" t="s">
         <v>28</v>
@@ -9030,10 +9012,10 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C308" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D308" s="11" t="s">
         <v>27</v>
@@ -9053,10 +9035,10 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C309" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D309" s="11" t="s">
         <v>27</v>
@@ -9076,10 +9058,10 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C310" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D310" s="11" t="s">
         <v>27</v>
@@ -9099,10 +9081,10 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C311" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D311" s="11" t="s">
         <v>27</v>
@@ -9122,10 +9104,10 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C312" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D312" s="11" t="s">
         <v>27</v>
@@ -9145,10 +9127,10 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C313" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D313" s="11" t="s">
         <v>27</v>
@@ -9168,10 +9150,10 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C314" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D314" s="11" t="s">
         <v>27</v>
@@ -9191,10 +9173,10 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C315" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D315" s="11" t="s">
         <v>27</v>
@@ -9214,10 +9196,10 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C316" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D316" s="11" t="s">
         <v>27</v>
@@ -9237,16 +9219,16 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C317" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D317" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E317" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F317" s="10" t="s">
         <v>28</v>
@@ -9260,10 +9242,10 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C318" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D318" s="11" t="s">
         <v>27</v>
@@ -9283,10 +9265,10 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C319" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D319" s="11" t="s">
         <v>27</v>
@@ -9306,10 +9288,10 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C320" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D320" s="11" t="s">
         <v>27</v>
@@ -9329,10 +9311,10 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C321" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D321" s="11" t="s">
         <v>27</v>
@@ -9352,10 +9334,10 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C322" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D322" s="11" t="s">
         <v>27</v>
@@ -9375,10 +9357,10 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
+        <v>352</v>
+      </c>
+      <c r="C323" t="s">
         <v>354</v>
-      </c>
-      <c r="C323" t="s">
-        <v>356</v>
       </c>
       <c r="D323" s="11" t="s">
         <v>27</v>
@@ -9398,10 +9380,10 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C324" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D324" s="11" t="s">
         <v>27</v>
@@ -9421,10 +9403,10 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C325" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D325" s="11" t="s">
         <v>27</v>
@@ -9444,10 +9426,10 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C326" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D326" s="11" t="s">
         <v>27</v>
@@ -9467,16 +9449,16 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C327" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D327" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E327" s="12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F327" s="10" t="s">
         <v>28</v>
@@ -9490,10 +9472,10 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C328" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D328" s="11" t="s">
         <v>27</v>
@@ -9513,10 +9495,10 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D329" s="11" t="s">
         <v>27</v>
@@ -9536,10 +9518,10 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C330" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D330" s="11" t="s">
         <v>27</v>
@@ -9559,10 +9541,10 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C331" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D331" s="11" t="s">
         <v>27</v>
@@ -9582,16 +9564,16 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C332" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D332" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E332" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F332" s="10" t="s">
         <v>28</v>
@@ -9605,10 +9587,10 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C333" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D333" s="11" t="s">
         <v>27</v>
@@ -9628,10 +9610,10 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C334" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D334" s="11" t="s">
         <v>27</v>
@@ -9651,10 +9633,10 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C335" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D335" s="11" t="s">
         <v>27</v>
@@ -9674,10 +9656,10 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C336" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D336" s="11" t="s">
         <v>27</v>
@@ -9697,10 +9679,10 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C337" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D337" s="11" t="s">
         <v>27</v>
@@ -9720,10 +9702,10 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C338" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D338" s="11" t="s">
         <v>27</v>
@@ -9743,10 +9725,10 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C339" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D339" s="11" t="s">
         <v>27</v>
@@ -9766,10 +9748,10 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C340" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D340" s="11" t="s">
         <v>27</v>
@@ -9789,10 +9771,10 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C341" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D341" s="11" t="s">
         <v>27</v>
@@ -9812,10 +9794,10 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C342" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D342" s="11" t="s">
         <v>27</v>
@@ -9835,10 +9817,10 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C343" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D343" s="11" t="s">
         <v>27</v>
@@ -9858,10 +9840,10 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C344" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D344" s="11" t="s">
         <v>27</v>
@@ -9881,10 +9863,10 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C345" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D345" s="11" t="s">
         <v>27</v>
@@ -9904,10 +9886,10 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C346" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D346" s="11" t="s">
         <v>27</v>
@@ -9927,10 +9909,10 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C347" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D347" s="11" t="s">
         <v>27</v>
@@ -9950,10 +9932,10 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C348" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D348" s="11" t="s">
         <v>27</v>
@@ -9973,10 +9955,10 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C349" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D349" s="11" t="s">
         <v>27</v>
@@ -9996,10 +9978,10 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C350" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D350" s="11" t="s">
         <v>27</v>
@@ -10019,10 +10001,10 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C351" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D351" s="11" t="s">
         <v>27</v>
@@ -10042,10 +10024,10 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C352" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D352" s="11" t="s">
         <v>27</v>
@@ -10065,16 +10047,16 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C353" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D353" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E353" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F353" s="10" t="s">
         <v>28</v>
@@ -10088,10 +10070,10 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C354" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D354" s="11" t="s">
         <v>27</v>
@@ -10111,10 +10093,10 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C355" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D355" s="11" t="s">
         <v>27</v>
@@ -10134,10 +10116,10 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C356" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D356" s="11" t="s">
         <v>27</v>
@@ -10157,10 +10139,10 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C357" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D357" s="11" t="s">
         <v>27</v>
@@ -10180,10 +10162,10 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C358" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D358" s="11" t="s">
         <v>27</v>
@@ -10203,10 +10185,10 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C359" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D359" s="11" t="s">
         <v>27</v>
@@ -10226,10 +10208,10 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C360" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D360" s="11" t="s">
         <v>27</v>
@@ -10249,10 +10231,10 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C361" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D361" s="11" t="s">
         <v>27</v>
@@ -10272,10 +10254,10 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C362" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D362" s="11" t="s">
         <v>27</v>
@@ -10295,10 +10277,10 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C363" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D363" s="11" t="s">
         <v>27</v>
@@ -10318,10 +10300,10 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C364" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D364" s="11" t="s">
         <v>27</v>
@@ -10341,10 +10323,10 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C365" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D365" s="11" t="s">
         <v>27</v>
@@ -10364,10 +10346,10 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C366" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D366" s="11" t="s">
         <v>27</v>
@@ -10387,10 +10369,10 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C367" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D367" s="11" t="s">
         <v>27</v>
@@ -10410,10 +10392,10 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C368" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D368" s="11" t="s">
         <v>27</v>
@@ -10433,16 +10415,16 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C369" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D369" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E369" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F369" s="10" t="s">
         <v>28</v>
@@ -10456,10 +10438,10 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C370" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D370" s="11" t="s">
         <v>27</v>
@@ -10479,10 +10461,10 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C371" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D371" s="11" t="s">
         <v>27</v>
@@ -10502,10 +10484,10 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C372" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D372" s="11" t="s">
         <v>27</v>
@@ -10525,10 +10507,10 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C373" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D373" s="11" t="s">
         <v>27</v>
@@ -10548,10 +10530,10 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C374" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D374" s="11" t="s">
         <v>27</v>
@@ -10571,10 +10553,10 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C375" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D375" s="11" t="s">
         <v>27</v>
@@ -10594,10 +10576,10 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C376" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D376" s="11" t="s">
         <v>27</v>
@@ -10617,10 +10599,10 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C377" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D377" s="11" t="s">
         <v>27</v>
@@ -10640,10 +10622,10 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C378" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D378" s="11" t="s">
         <v>27</v>
@@ -10663,10 +10645,10 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C379" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D379" s="11" t="s">
         <v>27</v>
@@ -10686,16 +10668,16 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C380" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D380" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E380" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F380" s="10" t="s">
         <v>28</v>
@@ -10709,10 +10691,10 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C381" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D381" s="11" t="s">
         <v>27</v>
@@ -10732,16 +10714,16 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C382" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D382" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E382" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F382" s="10" t="s">
         <v>28</v>
@@ -10755,10 +10737,10 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C383" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D383" s="11" t="s">
         <v>27</v>
@@ -10778,10 +10760,10 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C384" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D384" s="11" t="s">
         <v>27</v>
@@ -10801,10 +10783,10 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C385" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D385" s="11" t="s">
         <v>27</v>
@@ -10824,10 +10806,10 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C386" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D386" s="11" t="s">
         <v>27</v>
@@ -10847,10 +10829,10 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C387" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D387" s="11" t="s">
         <v>27</v>
@@ -10870,10 +10852,10 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C388" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D388" s="11" t="s">
         <v>27</v>
@@ -10893,10 +10875,10 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C389" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D389" s="11" t="s">
         <v>27</v>
@@ -10916,10 +10898,10 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C390" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D390" s="11" t="s">
         <v>27</v>
@@ -10939,10 +10921,10 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C391" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D391" s="11" t="s">
         <v>27</v>
@@ -10962,16 +10944,16 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C392" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D392" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E392" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F392" s="10" t="s">
         <v>28</v>
@@ -10985,10 +10967,10 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C393" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D393" s="11" t="s">
         <v>27</v>
@@ -11008,10 +10990,10 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C394" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D394" s="11" t="s">
         <v>27</v>
@@ -11031,10 +11013,10 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C395" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D395" s="11" t="s">
         <v>27</v>
@@ -11054,10 +11036,10 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C396" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D396" s="11" t="s">
         <v>27</v>
@@ -11077,10 +11059,10 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C397" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D397" s="11" t="s">
         <v>27</v>
@@ -11100,10 +11082,10 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C398" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D398" s="11" t="s">
         <v>27</v>
@@ -11123,10 +11105,10 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C399" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D399" s="11" t="s">
         <v>27</v>
@@ -11146,10 +11128,10 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C400" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D400" s="11" t="s">
         <v>27</v>
@@ -11169,10 +11151,10 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C401" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D401" s="11" t="s">
         <v>27</v>

--- a/appium-tests/reports/appium_e2e_test_report.xlsx
+++ b/appium-tests/reports/appium_e2e_test_report.xlsx
@@ -35,7 +35,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>22/7/2026, 6:43:43 pm</t>
+    <t>22/7/2026, 6:52:13 pm</t>
   </si>
   <si>
     <t>Target Platform</t>
@@ -47,7 +47,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>0.05 seconds</t>
+    <t>0.04 seconds</t>
   </si>
   <si>
     <t>Test Execution Summary Metrics</t>
@@ -98,7 +98,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>6:43:43 pm</t>
+    <t>6:52:13 pm</t>
   </si>
   <si>
     <t>N/A</t>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>28</v>
@@ -2029,7 +2029,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>28</v>
@@ -2121,7 +2121,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>28</v>
@@ -2144,7 +2144,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>28</v>
@@ -2397,7 +2397,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>28</v>
@@ -2673,7 +2673,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>28</v>
@@ -2742,7 +2742,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>28</v>
@@ -2834,7 +2834,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>28</v>
@@ -3708,7 +3708,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>28</v>
@@ -3800,7 +3800,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>28</v>
@@ -3892,7 +3892,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>28</v>
@@ -4122,7 +4122,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>28</v>
@@ -4674,7 +4674,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>28</v>
@@ -4697,7 +4697,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" s="10" t="s">
         <v>28</v>
@@ -4720,7 +4720,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>28</v>
@@ -4812,7 +4812,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>28</v>
@@ -5272,7 +5272,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>28</v>
@@ -5640,7 +5640,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>28</v>
@@ -5732,7 +5732,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>28</v>
@@ -6537,7 +6537,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F200" s="10" t="s">
         <v>28</v>
@@ -6560,7 +6560,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>28</v>
@@ -6652,7 +6652,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>28</v>
@@ -7618,7 +7618,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>28</v>
@@ -7733,7 +7733,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F252" s="10" t="s">
         <v>28</v>
@@ -7848,7 +7848,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>28</v>
@@ -8860,7 +8860,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F301" s="10" t="s">
         <v>28</v>
@@ -8998,7 +8998,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F307" s="10" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F327" s="10" t="s">
         <v>28</v>
@@ -9573,7 +9573,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F332" s="10" t="s">
         <v>28</v>
@@ -10585,7 +10585,7 @@
         <v>27</v>
       </c>
       <c r="E376" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F376" s="10" t="s">
         <v>28</v>
@@ -10723,7 +10723,7 @@
         <v>27</v>
       </c>
       <c r="E382" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F382" s="10" t="s">
         <v>28</v>
